--- a/ai/data/history/DataJobs_14082026.xlsx
+++ b/ai/data/history/DataJobs_14082026.xlsx
@@ -513,15 +513,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="27" customWidth="1" min="3" max="3"/>
-    <col width="71" customWidth="1" min="4" max="4"/>
-    <col width="83" customWidth="1" min="5" max="5"/>
-    <col width="35" customWidth="1" min="6" max="6"/>
+    <col width="124" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -535,7 +535,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report Generated: August 14, 2026 - 12:11 AM | Total Jobs: 25</t>
+          <t>Report Generated: August 14, 2026 - 11:54 PM | Total Jobs: 9</t>
         </is>
       </c>
     </row>
@@ -583,32 +583,32 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Brex</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Staff Software Engineer, Product Data Platform</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Remote - US</t>
+          <t>Seattle, Washington, United States</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>4-5 years, 5 years</t>
+          <t>8 years</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/twilio/jobs/8044650</t>
+          <t>https://www.brex.com/careers/8430197002?gh_jid=8430197002</t>
         </is>
       </c>
     </row>
@@ -618,32 +618,32 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>Keeper Security</t>
+          <t>ClickUp</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Business Intelligence</t>
+          <t>Principal Data Analyst, Product</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>El Dorado Hills, California, United States</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>5 years, 5 years</t>
+          <t>Assumed senior-level (seniority filter disabled)</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/keepersecurity/jobs/4185758009</t>
+          <t>https://jobs.ashbyhq.com/clickup/de33a412-8af0-4e80-832c-9876e7f9d11c</t>
         </is>
       </c>
     </row>
@@ -653,32 +653,32 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Airbnb</t>
+          <t>Runpod</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, People Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Remote - USA</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>4 years, 2 years</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>https://careers.airbnb.com/positions/7988010?gh_jid=7988010</t>
+          <t>https://jobs.ashbyhq.com/runpod/a63e8c2f-a319-4655-8179-b024a45db782</t>
         </is>
       </c>
     </row>
@@ -688,22 +688,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Lucid Motors (CA)</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Data Analyst Intern</t>
+          <t>Sr Associate - Warehouse Digital Transformation (S/4 Hana, DataBricks)</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Amsterdam, NH</t>
+          <t>US - Ohio - New Albany</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>https://job-boards.greenhouse.io/lucidmotors/jobs/5156608007</t>
+          <t>https://amgen.wd1.myworkdayjobs.com/careers/job/US---Ohio---New-Albany/Sr-Associate---Warehouse-Digital-Transformation--S-4-Hana--DataBricks-_R-252115</t>
         </is>
       </c>
     </row>
@@ -723,32 +723,32 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Anduril Industries (CA)</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Sr. Specialist Solutions Architect - Data Engineering &amp; Warehousing</t>
+          <t>Lead Data Analyst,  Manufacturing</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Costa Mesa, California, United States</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>8 years, 5 years</t>
+          <t>8 years, 2 years</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>https://databricks.com/company/careers/open-positions/job?gh_jid=8568122002</t>
+          <t>https://boards.greenhouse.io/andurilindustries/jobs/5212993007?gh_jid=5212993007</t>
         </is>
       </c>
     </row>
@@ -758,32 +758,32 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>Anduril Industries (CA)</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Staff, Analytics Engineer, GTM Data Science &amp; Analytics</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Costa Mesa, California, United States</t>
+          <t>Remote - US</t>
         </is>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>8 years</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>https://boards.greenhouse.io/andurilindustries/jobs/4743827007?gh_jid=4743827007</t>
+          <t>https://job-boards.greenhouse.io/twilio/jobs/8008538</t>
         </is>
       </c>
     </row>
@@ -793,32 +793,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>Coinbase</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering Platform</t>
+          <t>Data Analyst 3 - Supply Chain Planning</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Remote - USA</t>
+          <t>Seattle, WA</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>7 years</t>
+          <t>Not specified (Assumed 1-8 yrs)</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://www.coinbase.com/careers/positions/8082199?gh_jid=8082199</t>
+          <t>https://nordstrom.wd501.myworkdayjobs.com/nordstrom_careers/job/Seattle-WA/Data-Analyst-3---Supply-Chain-Planning_R-865543</t>
         </is>
       </c>
     </row>
@@ -828,32 +828,32 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Dropbox</t>
+          <t>Tyco (Johnson Controls)</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Senior Manager, Data Engineering</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Remote - US: Select locations</t>
+          <t>Milwaukee-Wisconsin-United States of America</t>
         </is>
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>8 years, 3 years</t>
+          <t>Assumed senior-level (seniority filter disabled)</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>https://jobs.dropbox.com/listing/8090062?gh_jid=8090062</t>
+          <t>https://jci.wd5.myworkdayjobs.com/jci/job/Milwaukee-Wisconsin-United-States-of-America/Senior-Data-Platform-Engineer_WD30275187</t>
         </is>
       </c>
     </row>
@@ -863,592 +863,32 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Waymo</t>
+          <t>Sharp HealthCare (CA)</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>Staff Business Intelligence Analyst, Resilience</t>
+          <t>Behavioral Health Therapist - Post Doctoral Fellow - COG/DBT OP - Sharp Mesa Vista Hospital - Temporary - FT - Day Shift</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>San Francisco, CA; Mountain View, CA</t>
+          <t>San Diego, CA</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>8 years</t>
+          <t>Not specified (Assumed 1-8 yrs)</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://careers.withwaymo.com/jobs?gh_jid=8078061</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>Scale AI</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>Staff Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA; New York, NY</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/scaleai/jobs/4649903005</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>Samsara</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Data Platform</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>Remote - US</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>4 years, 4 years</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>https://www.samsara.com/company/careers/roles/7922530?gh_jid=7922530</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>Anthropic</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>Data Engineering Manager, Product</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA | New York City, NY | Seattle, WA</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>8 years, 10 years</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/anthropic/jobs/5125387008</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>Upstart (CA)</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Staff Data Analyst, Servicing</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>United States | Remote</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>https://careers.upstart.com/jobs?gh_jid=7778782</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>Discord</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Staff Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
-        <is>
-          <t>San Francisco, CA</t>
-        </is>
-      </c>
-      <c r="F18" s="9" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/discord/jobs/8498984002</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>Riot Games</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Principal Data Engineer, Personalization - Central Product Insights</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>Los Angeles, USA</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>8 years, 8 years</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>https://www.riotgames.com/en/work-with-us/job/8049834?gh_jid=8049834</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-29</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>Thumbtack (CA)</t>
-        </is>
-      </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="E20" s="9" t="inlineStr">
-        <is>
-          <t>Remote, United States</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>4 years</t>
-        </is>
-      </c>
-      <c r="G20" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/thumbtack/d98e63a2-bbfb-48eb-8b73-abd3a8eb5976</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>Pinterest</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>Staff Software Engineer, Big Data Storage</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US; Remote, US</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>https://www.pinterestcareers.com/jobs/?gh_jid=7437356</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>Hims &amp; Hers Health (CA)</t>
-        </is>
-      </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>Staff Data Engineer</t>
-        </is>
-      </c>
-      <c r="E22" s="9" t="inlineStr">
-        <is>
-          <t>US Remote</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G22" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/hims-and-hers/22301cae-068f-47db-8d2a-91bebb59e52a</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>Dragos</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>Data Engineering Manager</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://job-boards.greenhouse.io/dragos/jobs/5365080008</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Helion Energy</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Data Platform</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Everett, WA</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>https://jobs.ashbyhq.com/helion/2c79c829-73cd-4558-9934-ea5f848a040a</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>SpaceX (CA)</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>Data Engineer (Starship)</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>Starbase, TX</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>2 years, 1 years</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/spacex/jobs/8569186002?gh_jid=8569186002</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>BILL</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>Staff Data Warehouse Engineer</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Draper, Utah, United States; San Jose, California, United States; United States</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G26" s="10" t="inlineStr">
-        <is>
-          <t>https://www.bill.com/job?6116018004&amp;gh_jid=6116018004</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>Zoox (Amazon) (CA)</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Enterprise Data &amp; AI</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>Foster City, CA</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>8 years</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>https://jobs.lever.co/zoox/e3465011-f94e-49e1-872e-68ec79c7db23</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Chime</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>Lead Data Analyst, MyPay</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>Chicago, IL, USA; New York, NY, USA; San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G28" s="10" t="inlineStr">
-        <is>
-          <t>https://boards.greenhouse.io/chime/jobs/8576707002?gh_jid=8576707002</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>Brex</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Product Data Platform</t>
-        </is>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
-        <is>
-          <t>San Francisco, California, United States</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>7 years</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>https://www.brex.com/careers/8430182002?gh_jid=8430182002</t>
+          <t>https://sharp.wd1.myworkdayjobs.com/external/job/San-Diego-CA/Behavioral-Health-Therapist---Post-Doctoral-Fellow---COG-DBT-OP---Sharp-Mesa-Vista-Hospital---Temporary---FT---Day-Shift_JR203536</t>
         </is>
       </c>
     </row>
@@ -1463,22 +903,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
